--- a/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_general.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.125</v>
+        <v>0.0401</v>
       </c>
       <c r="E2">
-        <v>0.655</v>
+        <v>-0.05860000000000001</v>
       </c>
       <c r="G2">
-        <v>0.1808604038630378</v>
+        <v>0.317653009610521</v>
       </c>
       <c r="H2">
-        <v>0.1808604038630378</v>
+        <v>0.317653009610521</v>
       </c>
       <c r="I2">
-        <v>0.3279192273924495</v>
+        <v>0.1547799696509864</v>
       </c>
       <c r="J2">
-        <v>0.307204917330513</v>
+        <v>0.1423615767371282</v>
       </c>
       <c r="K2">
-        <v>88.59999999999999</v>
+        <v>47.5</v>
       </c>
       <c r="L2">
-        <v>0.388937664618086</v>
+        <v>0.2402630247850278</v>
       </c>
       <c r="M2">
-        <v>16.7</v>
+        <v>18.95</v>
       </c>
       <c r="N2">
-        <v>0.03798044120991586</v>
+        <v>0.04444183864915572</v>
       </c>
       <c r="O2">
-        <v>0.1884875846501129</v>
+        <v>0.3989473684210526</v>
       </c>
       <c r="P2">
-        <v>9.720000000000001</v>
+        <v>17.4</v>
       </c>
       <c r="Q2">
-        <v>0.02210598135092108</v>
+        <v>0.04080675422138837</v>
       </c>
       <c r="R2">
-        <v>0.109706546275395</v>
+        <v>0.3663157894736842</v>
       </c>
       <c r="S2">
-        <v>6.980000000000002</v>
+        <v>1.550000000000001</v>
       </c>
       <c r="T2">
-        <v>0.4179640718562875</v>
+        <v>0.08179419525065967</v>
       </c>
       <c r="U2">
-        <v>300.2</v>
+        <v>299.5</v>
       </c>
       <c r="V2">
-        <v>0.6827382306117807</v>
+        <v>0.7023921200750469</v>
       </c>
       <c r="W2">
-        <v>0.07635956218219425</v>
+        <v>0.03521387797464601</v>
       </c>
       <c r="X2">
-        <v>0.04814289544782537</v>
+        <v>0.08137005607272095</v>
       </c>
       <c r="Y2">
-        <v>0.02821666673436888</v>
+        <v>-0.04615617809807494</v>
       </c>
       <c r="Z2">
-        <v>0.3127638687709808</v>
+        <v>0.1884213776776422</v>
       </c>
       <c r="AA2">
-        <v>0.09608259844976058</v>
+        <v>0.02682396441717106</v>
       </c>
       <c r="AB2">
-        <v>0.0481128011465996</v>
+        <v>0.08132500555006666</v>
       </c>
       <c r="AC2">
-        <v>0.04796979730316098</v>
+        <v>-0.0545010411328956</v>
       </c>
       <c r="AD2">
-        <v>0.544</v>
+        <v>0.538</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.544</v>
+        <v>0.538</v>
       </c>
       <c r="AG2">
-        <v>-299.656</v>
+        <v>-298.962</v>
       </c>
       <c r="AH2">
-        <v>0.001235678396525563</v>
+        <v>0.001260136132178443</v>
       </c>
       <c r="AI2">
-        <v>0.0004009895005616802</v>
+        <v>0.0004193499607931171</v>
       </c>
       <c r="AJ2">
-        <v>-2.13972751420982</v>
+        <v>-2.345940771198544</v>
       </c>
       <c r="AK2">
-        <v>-0.2836458913108504</v>
+        <v>-0.3039967949174223</v>
       </c>
       <c r="AL2">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AM2">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AN2">
-        <v>0.007111111111111111</v>
+        <v>0.01670807453416149</v>
       </c>
       <c r="AO2">
-        <v>6790.909090909092</v>
+        <v>2550</v>
       </c>
       <c r="AP2">
-        <v>-3.917071895424836</v>
+        <v>-9.284534161490683</v>
       </c>
       <c r="AQ2">
-        <v>6790.909090909092</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.125</v>
+        <v>0.0401</v>
       </c>
       <c r="E3">
-        <v>0.655</v>
+        <v>-0.05860000000000001</v>
       </c>
       <c r="G3">
-        <v>0.1808604038630378</v>
+        <v>0.317653009610521</v>
       </c>
       <c r="H3">
-        <v>0.1808604038630378</v>
+        <v>0.317653009610521</v>
       </c>
       <c r="I3">
-        <v>0.3279192273924495</v>
+        <v>0.1547799696509864</v>
       </c>
       <c r="J3">
-        <v>0.307204917330513</v>
+        <v>0.1423615767371282</v>
       </c>
       <c r="K3">
-        <v>88.59999999999999</v>
+        <v>47.5</v>
       </c>
       <c r="L3">
-        <v>0.388937664618086</v>
+        <v>0.2402630247850278</v>
       </c>
       <c r="M3">
-        <v>16.7</v>
+        <v>18.95</v>
       </c>
       <c r="N3">
-        <v>0.03798044120991586</v>
+        <v>0.04444183864915572</v>
       </c>
       <c r="O3">
-        <v>0.1884875846501129</v>
+        <v>0.3989473684210526</v>
       </c>
       <c r="P3">
-        <v>9.720000000000001</v>
+        <v>17.4</v>
       </c>
       <c r="Q3">
-        <v>0.02210598135092108</v>
+        <v>0.04080675422138837</v>
       </c>
       <c r="R3">
-        <v>0.109706546275395</v>
+        <v>0.3663157894736842</v>
       </c>
       <c r="S3">
-        <v>6.980000000000002</v>
+        <v>1.550000000000001</v>
       </c>
       <c r="T3">
-        <v>0.4179640718562875</v>
+        <v>0.08179419525065967</v>
       </c>
       <c r="U3">
-        <v>300.2</v>
+        <v>299.5</v>
       </c>
       <c r="V3">
-        <v>0.6827382306117807</v>
+        <v>0.7023921200750469</v>
       </c>
       <c r="W3">
-        <v>0.07635956218219425</v>
+        <v>0.03521387797464601</v>
       </c>
       <c r="X3">
-        <v>0.04814289544782537</v>
+        <v>0.08137005607272095</v>
       </c>
       <c r="Y3">
-        <v>0.02821666673436888</v>
+        <v>-0.04615617809807494</v>
       </c>
       <c r="Z3">
-        <v>0.3127638687709808</v>
+        <v>0.1884213776776422</v>
       </c>
       <c r="AA3">
-        <v>0.09608259844976058</v>
+        <v>0.02682396441717106</v>
       </c>
       <c r="AB3">
-        <v>0.0481128011465996</v>
+        <v>0.08132500555006666</v>
       </c>
       <c r="AC3">
-        <v>0.04796979730316098</v>
+        <v>-0.0545010411328956</v>
       </c>
       <c r="AD3">
-        <v>0.544</v>
+        <v>0.538</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.544</v>
+        <v>0.538</v>
       </c>
       <c r="AG3">
-        <v>-299.656</v>
+        <v>-298.962</v>
       </c>
       <c r="AH3">
-        <v>0.001235678396525563</v>
+        <v>0.001260136132178443</v>
       </c>
       <c r="AI3">
-        <v>0.0004009895005616802</v>
+        <v>0.0004193499607931171</v>
       </c>
       <c r="AJ3">
-        <v>-2.13972751420982</v>
+        <v>-2.345940771198544</v>
       </c>
       <c r="AK3">
-        <v>-0.2836458913108504</v>
+        <v>-0.3039967949174223</v>
       </c>
       <c r="AL3">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AM3">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AN3">
-        <v>0.007111111111111111</v>
+        <v>0.01670807453416149</v>
       </c>
       <c r="AO3">
-        <v>6790.909090909092</v>
+        <v>2550</v>
       </c>
       <c r="AP3">
-        <v>-3.917071895424836</v>
+        <v>-9.284534161490683</v>
       </c>
       <c r="AQ3">
-        <v>6790.909090909092</v>
+        <v>2550</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0401</v>
+        <v>0.0955</v>
       </c>
       <c r="E2">
-        <v>-0.05860000000000001</v>
+        <v>0.0688</v>
       </c>
       <c r="G2">
-        <v>0.317653009610521</v>
+        <v>0.09125259777064046</v>
       </c>
       <c r="H2">
-        <v>0.317653009610521</v>
+        <v>0.09125259777064046</v>
       </c>
       <c r="I2">
-        <v>0.1547799696509864</v>
+        <v>0.2366818308723039</v>
       </c>
       <c r="J2">
-        <v>0.1423615767371282</v>
+        <v>0.212305134213692</v>
       </c>
       <c r="K2">
-        <v>47.5</v>
+        <v>58.73</v>
       </c>
       <c r="L2">
-        <v>0.2402630247850278</v>
+        <v>0.2219157377668619</v>
       </c>
       <c r="M2">
-        <v>18.95</v>
+        <v>9.190000000000001</v>
       </c>
       <c r="N2">
-        <v>0.04444183864915572</v>
+        <v>0.01223538809745707</v>
       </c>
       <c r="O2">
-        <v>0.3989473684210526</v>
+        <v>0.1564788012940576</v>
       </c>
       <c r="P2">
-        <v>17.4</v>
+        <v>5.98</v>
       </c>
       <c r="Q2">
-        <v>0.04080675422138837</v>
+        <v>0.007961656237518308</v>
       </c>
       <c r="R2">
-        <v>0.3663157894736842</v>
+        <v>0.1018218968159374</v>
       </c>
       <c r="S2">
-        <v>1.550000000000001</v>
+        <v>3.210000000000001</v>
       </c>
       <c r="T2">
-        <v>0.08179419525065967</v>
+        <v>0.3492927094668118</v>
       </c>
       <c r="U2">
-        <v>299.5</v>
+        <v>183.77</v>
       </c>
       <c r="V2">
-        <v>0.7023921200750469</v>
+        <v>0.2446678205298895</v>
       </c>
       <c r="W2">
-        <v>0.03521387797464601</v>
+        <v>-1.0138909607891</v>
       </c>
       <c r="X2">
-        <v>0.08137005607272095</v>
+        <v>0.0729119771540185</v>
       </c>
       <c r="Y2">
-        <v>-0.04615617809807494</v>
+        <v>-1.086802937943119</v>
       </c>
       <c r="Z2">
-        <v>0.1884213776776422</v>
-      </c>
-      <c r="AA2">
-        <v>0.02682396441717106</v>
+        <v>0.2691069492942108</v>
       </c>
       <c r="AB2">
-        <v>0.08132500555006666</v>
-      </c>
-      <c r="AC2">
-        <v>-0.0545010411328956</v>
+        <v>0.07289049183787075</v>
       </c>
       <c r="AD2">
-        <v>0.538</v>
+        <v>0.539</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.0707672982238132</v>
       </c>
       <c r="AF2">
-        <v>0.538</v>
+        <v>0.6097672982238133</v>
       </c>
       <c r="AG2">
-        <v>-298.962</v>
+        <v>-183.1602327017762</v>
       </c>
       <c r="AH2">
-        <v>0.001260136132178443</v>
+        <v>0.0008111738396261944</v>
       </c>
       <c r="AI2">
-        <v>0.0004193499607931171</v>
+        <v>0.0004340815667319448</v>
       </c>
       <c r="AJ2">
-        <v>-2.345940771198544</v>
+        <v>-0.3224993973799324</v>
       </c>
       <c r="AK2">
-        <v>-0.3039967949174223</v>
+        <v>-0.1500133236225127</v>
       </c>
       <c r="AL2">
-        <v>0.012</v>
+        <v>4.961</v>
       </c>
       <c r="AM2">
-        <v>0.012</v>
+        <v>4.961</v>
       </c>
       <c r="AN2">
-        <v>0.01670807453416149</v>
+        <v>0.00838623350759273</v>
       </c>
       <c r="AO2">
-        <v>2550</v>
+        <v>12.62043942753477</v>
       </c>
       <c r="AP2">
-        <v>-9.284534161490683</v>
+        <v>-2.849767125681108</v>
       </c>
       <c r="AQ2">
-        <v>2550</v>
+        <v>12.62043942753477</v>
       </c>
     </row>
     <row r="3">
@@ -713,130 +707,246 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>QDM International Inc. (OTCPK:QDMI)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>0.009009009009009009</v>
+      </c>
+      <c r="H3">
+        <v>0.009009009009009009</v>
+      </c>
+      <c r="I3">
+        <v>0.2951074847486915</v>
+      </c>
+      <c r="J3">
+        <v>0.2557598201155326</v>
+      </c>
+      <c r="K3">
+        <v>1.43</v>
+      </c>
+      <c r="L3">
+        <v>0.2576576576576576</v>
+      </c>
+      <c r="M3">
+        <v>-0</v>
+      </c>
+      <c r="N3">
+        <v>-0</v>
+      </c>
+      <c r="O3">
+        <v>-0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>-0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>5.47</v>
+      </c>
+      <c r="V3">
+        <v>0.01663119489206446</v>
+      </c>
+      <c r="W3">
+        <v>-2.072463768115942</v>
+      </c>
+      <c r="X3">
+        <v>0.07289686919384879</v>
+      </c>
+      <c r="Y3">
+        <v>-2.145360637309791</v>
+      </c>
+      <c r="AB3">
+        <v>0.07289197494287958</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0.0707672982238132</v>
+      </c>
+      <c r="AF3">
+        <v>0.0707672982238132</v>
+      </c>
+      <c r="AG3">
+        <v>-5.399232701776187</v>
+      </c>
+      <c r="AH3">
+        <v>0.0002151172847515053</v>
+      </c>
+      <c r="AI3">
+        <v>0.02289635271619491</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.01669001513309806</v>
+      </c>
+      <c r="AK3">
+        <v>2.269316783408977</v>
+      </c>
+      <c r="AL3">
+        <v>0.001</v>
+      </c>
+      <c r="AM3">
+        <v>0.001</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>1610</v>
+      </c>
+      <c r="AP3">
+        <v>-3.229206161349394</v>
+      </c>
+      <c r="AQ3">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Asia Financial Holdings Limited (SEHK:662)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.0401</v>
-      </c>
-      <c r="E3">
-        <v>-0.05860000000000001</v>
-      </c>
-      <c r="G3">
-        <v>0.317653009610521</v>
-      </c>
-      <c r="H3">
-        <v>0.317653009610521</v>
-      </c>
-      <c r="I3">
-        <v>0.1547799696509864</v>
-      </c>
-      <c r="J3">
-        <v>0.1423615767371282</v>
-      </c>
-      <c r="K3">
-        <v>47.5</v>
-      </c>
-      <c r="L3">
-        <v>0.2402630247850278</v>
-      </c>
-      <c r="M3">
-        <v>18.95</v>
-      </c>
-      <c r="N3">
-        <v>0.04444183864915572</v>
-      </c>
-      <c r="O3">
-        <v>0.3989473684210526</v>
-      </c>
-      <c r="P3">
-        <v>17.4</v>
-      </c>
-      <c r="Q3">
-        <v>0.04080675422138837</v>
-      </c>
-      <c r="R3">
-        <v>0.3663157894736842</v>
-      </c>
-      <c r="S3">
-        <v>1.550000000000001</v>
-      </c>
-      <c r="T3">
-        <v>0.08179419525065967</v>
-      </c>
-      <c r="U3">
-        <v>299.5</v>
-      </c>
-      <c r="V3">
-        <v>0.7023921200750469</v>
-      </c>
-      <c r="W3">
-        <v>0.03521387797464601</v>
-      </c>
-      <c r="X3">
-        <v>0.08137005607272095</v>
-      </c>
-      <c r="Y3">
-        <v>-0.04615617809807494</v>
-      </c>
-      <c r="Z3">
-        <v>0.1884213776776422</v>
-      </c>
-      <c r="AA3">
-        <v>0.02682396441717106</v>
-      </c>
-      <c r="AB3">
-        <v>0.08132500555006666</v>
-      </c>
-      <c r="AC3">
-        <v>-0.0545010411328956</v>
-      </c>
-      <c r="AD3">
-        <v>0.538</v>
-      </c>
-      <c r="AE3">
+      <c r="D4">
+        <v>0.0955</v>
+      </c>
+      <c r="E4">
+        <v>0.0688</v>
+      </c>
+      <c r="G4">
+        <v>0.09301428020069472</v>
+      </c>
+      <c r="H4">
+        <v>0.09301428020069472</v>
+      </c>
+      <c r="I4">
+        <v>0.235430335777692</v>
+      </c>
+      <c r="J4">
+        <v>0.2183254456864001</v>
+      </c>
+      <c r="K4">
+        <v>57.3</v>
+      </c>
+      <c r="L4">
+        <v>0.2211501350829795</v>
+      </c>
+      <c r="M4">
+        <v>9.190000000000001</v>
+      </c>
+      <c r="N4">
+        <v>0.02176693510184747</v>
+      </c>
+      <c r="O4">
+        <v>0.1603839441535777</v>
+      </c>
+      <c r="P4">
+        <v>5.98</v>
+      </c>
+      <c r="Q4">
+        <v>0.01416390336333491</v>
+      </c>
+      <c r="R4">
+        <v>0.1043630017452007</v>
+      </c>
+      <c r="S4">
+        <v>3.210000000000001</v>
+      </c>
+      <c r="T4">
+        <v>0.3492927094668118</v>
+      </c>
+      <c r="U4">
+        <v>178.3</v>
+      </c>
+      <c r="V4">
+        <v>0.4223117006158219</v>
+      </c>
+      <c r="W4">
+        <v>0.04468184653774173</v>
+      </c>
+      <c r="X4">
+        <v>0.0729270851141882</v>
+      </c>
+      <c r="Y4">
+        <v>-0.02824523857644647</v>
+      </c>
+      <c r="Z4">
+        <v>0.263463482192065</v>
+      </c>
+      <c r="AA4">
+        <v>0.05752078217167353</v>
+      </c>
+      <c r="AB4">
+        <v>0.0728890087328619</v>
+      </c>
+      <c r="AC4">
+        <v>-0.01536822656118837</v>
+      </c>
+      <c r="AD4">
+        <v>0.539</v>
+      </c>
+      <c r="AE4">
         <v>0</v>
       </c>
-      <c r="AF3">
-        <v>0.538</v>
-      </c>
-      <c r="AG3">
-        <v>-298.962</v>
-      </c>
-      <c r="AH3">
-        <v>0.001260136132178443</v>
-      </c>
-      <c r="AI3">
-        <v>0.0004193499607931171</v>
-      </c>
-      <c r="AJ3">
-        <v>-2.345940771198544</v>
-      </c>
-      <c r="AK3">
-        <v>-0.3039967949174223</v>
-      </c>
-      <c r="AL3">
-        <v>0.012</v>
-      </c>
-      <c r="AM3">
-        <v>0.012</v>
-      </c>
-      <c r="AN3">
-        <v>0.01670807453416149</v>
-      </c>
-      <c r="AO3">
-        <v>2550</v>
-      </c>
-      <c r="AP3">
-        <v>-9.284534161490683</v>
-      </c>
-      <c r="AQ3">
-        <v>2550</v>
+      <c r="AF4">
+        <v>0.539</v>
+      </c>
+      <c r="AG4">
+        <v>-177.761</v>
+      </c>
+      <c r="AH4">
+        <v>0.00127501839196289</v>
+      </c>
+      <c r="AI4">
+        <v>0.0003845498020531678</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.7272202880882349</v>
+      </c>
+      <c r="AK4">
+        <v>-0.1453080462570065</v>
+      </c>
+      <c r="AL4">
+        <v>4.96</v>
+      </c>
+      <c r="AM4">
+        <v>4.96</v>
+      </c>
+      <c r="AN4">
+        <v>0.008610223642172524</v>
+      </c>
+      <c r="AO4">
+        <v>12.29838709677419</v>
+      </c>
+      <c r="AP4">
+        <v>-2.839632587859425</v>
+      </c>
+      <c r="AQ4">
+        <v>12.29838709677419</v>
       </c>
     </row>
   </sheetData>
